--- a/python/CVPROJECT.xlsx
+++ b/python/CVPROJECT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\captsoneFiles\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56485ABB-1057-4AE6-BDF6-D9BFF4279EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD2D914-8AA2-4773-A2BD-1EE86D8BB20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>HussainArsiwala</t>
   </si>
@@ -58,6 +58,132 @@
   </si>
   <si>
     <t>B129</t>
+  </si>
+  <si>
+    <t>Tanisha</t>
+  </si>
+  <si>
+    <t>Yash K</t>
+  </si>
+  <si>
+    <t>Soumik</t>
+  </si>
+  <si>
+    <t>Saanya</t>
+  </si>
+  <si>
+    <t>Preksha</t>
+  </si>
+  <si>
+    <t>Tapur</t>
+  </si>
+  <si>
+    <t>Prady</t>
+  </si>
+  <si>
+    <t>Soham</t>
+  </si>
+  <si>
+    <t>Pratyush</t>
+  </si>
+  <si>
+    <t>Dhuri</t>
+  </si>
+  <si>
+    <t>Hardik</t>
+  </si>
+  <si>
+    <t>Ketan</t>
+  </si>
+  <si>
+    <t>Zeeshan</t>
+  </si>
+  <si>
+    <t>Ahmed</t>
+  </si>
+  <si>
+    <t>Anushka</t>
+  </si>
+  <si>
+    <t>Nikita</t>
+  </si>
+  <si>
+    <t>Yashaswini</t>
+  </si>
+  <si>
+    <t>Adit K</t>
+  </si>
+  <si>
+    <t>Suhani</t>
+  </si>
+  <si>
+    <t>Zaid</t>
+  </si>
+  <si>
+    <t>Nitya</t>
+  </si>
+  <si>
+    <t>B148</t>
+  </si>
+  <si>
+    <t>B171</t>
+  </si>
+  <si>
+    <t>N100</t>
+  </si>
+  <si>
+    <t>B130</t>
+  </si>
+  <si>
+    <t>B194</t>
+  </si>
+  <si>
+    <t>B217</t>
+  </si>
+  <si>
+    <t>N101</t>
+  </si>
+  <si>
+    <t>B131</t>
+  </si>
+  <si>
+    <t>B240</t>
+  </si>
+  <si>
+    <t>B263</t>
+  </si>
+  <si>
+    <t>N102</t>
+  </si>
+  <si>
+    <t>B132</t>
+  </si>
+  <si>
+    <t>B286</t>
+  </si>
+  <si>
+    <t>B309</t>
+  </si>
+  <si>
+    <t>N103</t>
+  </si>
+  <si>
+    <t>B133</t>
+  </si>
+  <si>
+    <t>B332</t>
+  </si>
+  <si>
+    <t>B355</t>
+  </si>
+  <si>
+    <t>N104</t>
+  </si>
+  <si>
+    <t>B134</t>
+  </si>
+  <si>
+    <t>B378</t>
   </si>
 </sst>
 </file>
@@ -381,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -443,6 +569,237 @@
         <v>10</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>19</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>20</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>21</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
